--- a/Assets/Data/Map1010.xlsx
+++ b/Assets/Data/Map1010.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="17">
   <si>
     <t>_</t>
   </si>
@@ -76,10 +76,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -97,29 +97,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -127,22 +105,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -157,8 +121,83 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -172,6 +211,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -180,62 +234,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -250,7 +250,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -262,37 +418,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -304,133 +430,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -441,33 +441,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -488,11 +461,48 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -512,32 +522,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -549,145 +549,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1407,19 +1407,45 @@
       <c r="AB2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="AC2" s="2"/>
-      <c r="AD2" s="2"/>
-      <c r="AE2" s="2"/>
-      <c r="AF2" s="2"/>
-      <c r="AG2" s="2"/>
-      <c r="AH2" s="2"/>
-      <c r="AI2" s="2"/>
-      <c r="AJ2" s="2"/>
-      <c r="AK2" s="2"/>
-      <c r="AL2" s="2"/>
-      <c r="AM2" s="2"/>
-      <c r="AN2" s="2"/>
-      <c r="AO2" s="2"/>
+      <c r="AC2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO2" s="2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" spans="1:41">
       <c r="A3">
@@ -1453,9 +1479,7 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
       <c r="AA3" s="2"/>
-      <c r="AB3" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="AB3" s="2"/>
       <c r="AC3" s="2"/>
       <c r="AD3" s="2"/>
       <c r="AE3" s="2"/>
@@ -1468,7 +1492,9 @@
       <c r="AL3" s="2"/>
       <c r="AM3" s="2"/>
       <c r="AN3" s="2"/>
-      <c r="AO3" s="2"/>
+      <c r="AO3" s="2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:41">
       <c r="A4">
@@ -1502,9 +1528,7 @@
       <c r="Y4" s="2"/>
       <c r="Z4" s="2"/>
       <c r="AA4" s="2"/>
-      <c r="AB4" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="AB4" s="2"/>
       <c r="AC4" s="2"/>
       <c r="AD4" s="2"/>
       <c r="AE4" s="2"/>
@@ -1517,7 +1541,9 @@
       <c r="AL4" s="2"/>
       <c r="AM4" s="2"/>
       <c r="AN4" s="2"/>
-      <c r="AO4" s="2"/>
+      <c r="AO4" s="2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:41">
       <c r="A5">
@@ -1551,9 +1577,7 @@
       <c r="Y5" s="2"/>
       <c r="Z5" s="2"/>
       <c r="AA5" s="2"/>
-      <c r="AB5" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="AB5" s="2"/>
       <c r="AC5" s="2"/>
       <c r="AD5" s="2"/>
       <c r="AE5" s="2"/>
@@ -1566,7 +1590,9 @@
       <c r="AL5" s="2"/>
       <c r="AM5" s="2"/>
       <c r="AN5" s="2"/>
-      <c r="AO5" s="2"/>
+      <c r="AO5" s="2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:41">
       <c r="A6">
@@ -1600,9 +1626,7 @@
       <c r="Y6" s="2"/>
       <c r="Z6" s="2"/>
       <c r="AA6" s="2"/>
-      <c r="AB6" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="AB6" s="2"/>
       <c r="AC6" s="2"/>
       <c r="AD6" s="2"/>
       <c r="AE6" s="2"/>
@@ -1615,7 +1639,9 @@
       <c r="AL6" s="2"/>
       <c r="AM6" s="2"/>
       <c r="AN6" s="2"/>
-      <c r="AO6" s="2"/>
+      <c r="AO6" s="2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:41">
       <c r="A7">
@@ -1649,9 +1675,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
       <c r="AA7" s="2"/>
-      <c r="AB7" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="AB7" s="2"/>
       <c r="AC7" s="2"/>
       <c r="AD7" s="2"/>
       <c r="AE7" s="2"/>
@@ -1664,7 +1688,9 @@
       <c r="AL7" s="2"/>
       <c r="AM7" s="2"/>
       <c r="AN7" s="2"/>
-      <c r="AO7" s="2"/>
+      <c r="AO7" s="2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:41">
       <c r="A8">
@@ -1698,9 +1724,7 @@
       <c r="Y8" s="2"/>
       <c r="Z8" s="2"/>
       <c r="AA8" s="2"/>
-      <c r="AB8" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="AB8" s="2"/>
       <c r="AC8" s="2"/>
       <c r="AD8" s="2"/>
       <c r="AE8" s="2"/>
@@ -1713,7 +1737,9 @@
       <c r="AL8" s="2"/>
       <c r="AM8" s="2"/>
       <c r="AN8" s="2"/>
-      <c r="AO8" s="2"/>
+      <c r="AO8" s="2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:41">
       <c r="A9">
@@ -1747,9 +1773,7 @@
       <c r="Y9" s="2"/>
       <c r="Z9" s="2"/>
       <c r="AA9" s="2"/>
-      <c r="AB9" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="AB9" s="2"/>
       <c r="AC9" s="2"/>
       <c r="AD9" s="2"/>
       <c r="AE9" s="2"/>
@@ -1762,7 +1786,9 @@
       <c r="AL9" s="2"/>
       <c r="AM9" s="2"/>
       <c r="AN9" s="2"/>
-      <c r="AO9" s="2"/>
+      <c r="AO9" s="2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:41">
       <c r="A10">
@@ -1796,9 +1822,7 @@
       <c r="Y10" s="2"/>
       <c r="Z10" s="2"/>
       <c r="AA10" s="2"/>
-      <c r="AB10" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="AB10" s="2"/>
       <c r="AC10" s="2"/>
       <c r="AD10" s="2"/>
       <c r="AE10" s="2"/>
@@ -1811,7 +1835,9 @@
       <c r="AL10" s="2"/>
       <c r="AM10" s="2"/>
       <c r="AN10" s="2"/>
-      <c r="AO10" s="2"/>
+      <c r="AO10" s="2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:41">
       <c r="A11">
@@ -1845,9 +1871,7 @@
       <c r="Y11" s="2"/>
       <c r="Z11" s="2"/>
       <c r="AA11" s="2"/>
-      <c r="AB11" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="AB11" s="2"/>
       <c r="AC11" s="2"/>
       <c r="AD11" s="2"/>
       <c r="AE11" s="2"/>
@@ -1860,7 +1884,9 @@
       <c r="AL11" s="2"/>
       <c r="AM11" s="2"/>
       <c r="AN11" s="2"/>
-      <c r="AO11" s="2"/>
+      <c r="AO11" s="2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:41">
       <c r="A12">
@@ -1869,84 +1895,32 @@
       <c r="B12" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="S12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="U12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="W12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="X12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB12" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+      <c r="T12" s="2"/>
+      <c r="U12" s="2"/>
+      <c r="V12" s="2"/>
+      <c r="W12" s="2"/>
+      <c r="X12" s="2"/>
+      <c r="Y12" s="2"/>
+      <c r="Z12" s="2"/>
+      <c r="AA12" s="2"/>
+      <c r="AB12" s="2"/>
       <c r="AC12" s="2"/>
       <c r="AD12" s="2"/>
       <c r="AE12" s="2"/>
@@ -1959,13 +1933,17 @@
       <c r="AL12" s="2"/>
       <c r="AM12" s="2"/>
       <c r="AN12" s="2"/>
-      <c r="AO12" s="2"/>
+      <c r="AO12" s="2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:41">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="2"/>
+      <c r="B13" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -2004,52 +1982,134 @@
       <c r="AL13" s="2"/>
       <c r="AM13" s="2"/>
       <c r="AN13" s="2"/>
-      <c r="AO13" s="2"/>
+      <c r="AO13" s="2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:41">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2"/>
-      <c r="S14" s="2"/>
-      <c r="T14" s="2"/>
-      <c r="U14" s="2"/>
-      <c r="V14" s="2"/>
-      <c r="W14" s="2"/>
-      <c r="X14" s="2"/>
-      <c r="Y14" s="2"/>
-      <c r="Z14" s="2"/>
-      <c r="AA14" s="2"/>
-      <c r="AB14" s="2"/>
-      <c r="AC14" s="2"/>
-      <c r="AD14" s="2"/>
-      <c r="AE14" s="2"/>
-      <c r="AF14" s="2"/>
-      <c r="AG14" s="2"/>
-      <c r="AH14" s="2"/>
-      <c r="AI14" s="2"/>
-      <c r="AJ14" s="2"/>
-      <c r="AK14" s="2"/>
-      <c r="AL14" s="2"/>
-      <c r="AM14" s="2"/>
-      <c r="AN14" s="2"/>
-      <c r="AO14" s="2"/>
+      <c r="B14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="V14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="W14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO14" s="2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:41">
       <c r="A15">
